--- a/teacher_feedback_forms/022_tutoring_services_feedback_form--teacher_feedback_forms.xlsx
+++ b/teacher_feedback_forms/022_tutoring_services_feedback_form--teacher_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Page Number</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Page Count</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Page Size</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Page Numbering</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Student Name</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>teacher_name</t>
+          <t>teacher_name_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Teacher Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>form_submit_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Form Submit 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_cancel</t>
+          <t>form_cancel_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Form Cancel 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>teacher_name_choices</t>
+          <t>teacher_name_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>teacher_name_choices</t>
+          <t>teacher_name_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
